--- a/Assets/Documents/Definición Examen Final.xlsx
+++ b/Assets/Documents/Definición Examen Final.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="Hoja 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F26"/>
+  <dimension ref="B2:F27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="44.88" customWidth="1" style="24" min="3" max="3"/>
@@ -550,7 +550,11 @@
           <t>El juego abre el menú y espera recién cuando colocas tu nickname y apretás Play se conecta a internet. Si dejás el campo vacío y apretás Play, el juego te asigna automáticamente un nombre.</t>
         </is>
       </c>
-      <c r="F3" s="7" t="n"/>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>NetworkManager.cs:42</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="B4" s="8" t="n">
@@ -569,7 +573,11 @@
           <t>Cuando tocas el boton de unirte a una sala de la lista</t>
         </is>
       </c>
-      <c r="F4" s="12" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>MatchmakingManager.cs:35</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="8" t="n">
@@ -588,7 +596,11 @@
           <t>Ves una lista de botones de unirse, uno por sala, cada uno muestra el nombre, cuántos jugadores hay (2/4) y si está llena el botón dice FULL y no se puede apretar.</t>
         </is>
       </c>
-      <c r="F5" s="12" t="n"/>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>RoomObject.cs:34</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="8" t="n">
@@ -607,7 +619,11 @@
           <t>Sincronizamos todo lo que el auto hace (posición, velocidad, si está usando turbo o derrape) mediante Delta Sync. Todos ven una pantalla de loading; el host espera a que todos los autos aparezcan en la pista antes de arrancar el countdown. Si alguien tarda demasiado, hay un timeout y la carrera arranca igual sin él.</t>
         </is>
       </c>
-      <c r="F6" s="12" t="n"/>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>CarNetworkSync.cs:117 (OnPhotonSerializeView)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="8" t="n">
@@ -626,7 +642,11 @@
           <t>RPC se usan en las colisiones destructivas (primero al Master Client para validar, luego a todos para explotar). Los RaiseEvents se usan para avisar la hora de largada de la carrera y para mandar las posiciones finales del podio</t>
         </is>
       </c>
-      <c r="F7" s="12" t="n"/>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>CarClashMinigame.cs / RaceManager.cs</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="8" t="n">
@@ -645,7 +665,11 @@
           <t>Los choques leves se calculan en la PC de cada uno (client-side), y los choques mortales requieren interacción con el Master Client. Ademas estos interactuan combatiendo con los Power ups</t>
         </is>
       </c>
-      <c r="F8" s="12" t="n"/>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>CarArcadeCollision.cs</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="8" t="n">
@@ -664,7 +688,11 @@
           <t>El juego cubre todo el ciclo: los jugadores cargan la pista todos juntos, esperan el semáforo, corren agarrando cajas, cruzan la meta, se calcula quién ganó y se muestra el podio</t>
         </is>
       </c>
-      <c r="F9" s="12" t="n"/>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>RaceManager.cs</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="8" t="n">
@@ -683,7 +711,11 @@
           <t>Se muestra en UI los problemas basicos de desconexióny errores</t>
         </is>
       </c>
-      <c r="F10" s="12" t="n"/>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>NetworkManager.cs / ReconnectionPanel.cs</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="8" t="n">
@@ -763,7 +795,11 @@
           <t>Photon promueve automáticamente al siguiente jugador como MC, y todos los sistemas usan PhotonNetwork.IsMasterClient</t>
         </is>
       </c>
-      <c r="F14" s="25" t="n"/>
+      <c r="F14" s="25" t="inlineStr">
+        <is>
+          <t>RaceManager.cs (OnMasterClientSwitched)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="14" t="n">
@@ -782,7 +818,11 @@
           <t>Si hay lag o se pierden paquetes, usamos "Extrapolación" (el juego adivina dónde está el auto con un límite de seguridad de 0.5s para no salir volando)</t>
         </is>
       </c>
-      <c r="F15" s="25" t="n"/>
+      <c r="F15" s="25" t="inlineStr">
+        <is>
+          <t>CarNetworkSync.cs</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="14" t="n">
@@ -801,7 +841,11 @@
           <t>El jugador escribe su nombre,mostrándose en un cartelito 3D flotando arriba del auto en la pista</t>
         </is>
       </c>
-      <c r="F16" s="25" t="n"/>
+      <c r="F16" s="25" t="inlineStr">
+        <is>
+          <t>CarNicknameLabel.cs</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="14" t="n">
@@ -817,10 +861,14 @@
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t>El contenedor visual (la rotación y aspecto de los autos) se sincroniza</t>
-        </is>
-      </c>
-      <c r="F17" s="25" t="n"/>
+          <t>El contenedor visual (la rotación y aspecto de los autos) se sincroniza. Cada bot recibe un color de auto fijo y distinto entre sí (vía Instantiation Data), para no repetir la skin que el jugador humano tiene elegida.</t>
+        </is>
+      </c>
+      <c r="F17" s="25" t="inlineStr">
+        <is>
+          <t>CarSkinLoader.cs</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="14" t="n">
@@ -839,7 +887,11 @@
           <t>Enviamos comandos como derrape o Iturbo mediante la red. Al recibirlos, el auto rival activa esos estados visuales/animaciones. Se agregan a esta sincronizacion de strech and squash de los vehiculos</t>
         </is>
       </c>
-      <c r="F18" s="25" t="n"/>
+      <c r="F18" s="25" t="inlineStr">
+        <is>
+          <t>CarNetworkSync.cs / CarStretchSquash.cs</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="14" t="n">
@@ -858,7 +910,11 @@
           <t>Usamos los relojes universales de Photon. La largada se sincroniza con PhotonNetwork.Time para que todos arranquen a la vez, y el podio se define milimétricamente con Timestamp cuando cruzan la meta. Por otro lado el minijuego de spacebar.</t>
         </is>
       </c>
-      <c r="F19" s="25" t="n"/>
+      <c r="F19" s="25" t="inlineStr">
+        <is>
+          <t>RaceManager.cs:117-199</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="B20" s="14" t="n">
@@ -946,7 +1002,11 @@
           <t>Guardamos el perfil del jugador usando serialización Binaria</t>
         </is>
       </c>
-      <c r="F23" s="25" t="n"/>
+      <c r="F23" s="25" t="inlineStr">
+        <is>
+          <t>LocalSaveManager.cs</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="B24" s="14" t="n">
@@ -988,7 +1048,11 @@
           <t>Nos conectamos a una API de puntajes (Leaderboards), usando Firebase</t>
         </is>
       </c>
-      <c r="F25" s="25" t="n"/>
+      <c r="F25" s="25" t="inlineStr">
+        <is>
+          <t>LeaderboardService.cs</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="B26" s="20" t="n">
@@ -1007,7 +1071,36 @@
           <t>Usamos la herramienta en la nube de Unity para poder desactivar mapas, skins o power-ups que estén rotos en pleno juego.</t>
         </is>
       </c>
-      <c r="F26" s="23" t="n"/>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>LiveOpsConfig.cs</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>Localización Multi-idioma (ES/EN)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>El juego está traducido a Español e Inglés. Se cambia de idioma en tiempo real desde Configuración &gt; Idioma (botones ES/EN) sin reiniciar: un ScriptableObject (LanguageTable) mapea cada clave a su traducción por idioma, LocalizationManager expone el idioma activo y dispara un evento, y cada texto (LocalizedText) se re-traduce solo. El idioma se guarda en PlayerPrefs y se restaura entre sesiones.</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>LocalizationManager.cs / LanguageTable.cs / LocalizedText.cs / SettingsManager.cs</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
